--- a/results/2045_BS0006/Scenario_comparison_region.xlsx
+++ b/results/2045_BS0006/Scenario_comparison_region.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario final_26_03_09" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scenario REG-BASE" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,11 +504,11 @@
         <v>62.5</v>
       </c>
       <c r="E3" t="n">
-        <v>11.72805800016099</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>74.22805800016098</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="4">
@@ -564,20 +564,20 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.675607501223467</v>
+        <v>18.12867710584072</v>
       </c>
       <c r="C6" t="n">
-        <v>23.07823581831755</v>
+        <v>39.55492109061032</v>
       </c>
       <c r="D6" t="n">
-        <v>38.97272649175476</v>
+        <v>48.35485627454377</v>
       </c>
       <c r="E6" t="n">
-        <v>35.03835242734387</v>
+        <v>54.26091883617155</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>101.7649222386397</v>
+        <v>160.2993733071664</v>
       </c>
     </row>
     <row r="7">
@@ -639,14 +639,14 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>61.89415436528028</v>
+        <v>68.43987736188659</v>
       </c>
       <c r="E9" t="n">
-        <v>61.12553102617063</v>
+        <v>67.37218403958954</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>123.0196853914509</v>
+        <v>135.8120614014761</v>
       </c>
     </row>
     <row r="10">
@@ -659,40 +659,40 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>34.68173261341614</v>
+        <v>25.97279222248014</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1.295380774386549</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>34.68173261341614</v>
+        <v>27.26817299686669</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>BtL_holz</t>
+          <t>BtL_Holz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>8.21689543674508</v>
       </c>
       <c r="C11" t="n">
-        <v>58.49783633736904</v>
+        <v>50.96473426760409</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>96.98476775427935</v>
+        <v>89.79629519481406</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>155.4826040916484</v>
+        <v>148.9779248991632</v>
       </c>
     </row>
     <row r="12">
@@ -702,20 +702,20 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83.8479641107306</v>
+        <v>75.63106867398552</v>
       </c>
       <c r="C12" t="n">
-        <v>108.0539089735898</v>
+        <v>115.5870110433548</v>
       </c>
       <c r="D12" t="n">
-        <v>100.7526510073059</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>41.87024455588045</v>
+        <v>49.05871711534573</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>334.5247686475068</v>
+        <v>240.2767968326861</v>
       </c>
     </row>
     <row r="13">
@@ -750,20 +750,20 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>825.4190514629762</v>
+        <v>804.7475478133201</v>
       </c>
       <c r="C14" t="n">
-        <v>686.4184734972937</v>
+        <v>792.8557309465983</v>
       </c>
       <c r="D14" t="n">
-        <v>630.312984683159</v>
+        <v>732.9107676681892</v>
       </c>
       <c r="E14" t="n">
-        <v>727.0648443169591</v>
+        <v>896.4599727843945</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>2869.215353960388</v>
+        <v>3226.974019212502</v>
       </c>
     </row>
     <row r="15">
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>426.2968121078734</v>
+        <v>396.8760978546129</v>
       </c>
       <c r="C15" t="n">
-        <v>513.4485899945843</v>
+        <v>490.2880272606249</v>
       </c>
       <c r="D15" t="n">
-        <v>445.0097358534619</v>
+        <v>455.5887692367443</v>
       </c>
       <c r="E15" t="n">
-        <v>453.709649937457</v>
+        <v>419.8119451379845</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>1838.464787893377</v>
+        <v>1762.564839489967</v>
       </c>
     </row>
     <row r="16">
@@ -819,26 +819,26 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53.78517250570003</v>
+        <v>54.32917347828755</v>
       </c>
       <c r="C17" t="n">
-        <v>116.7603728547275</v>
+        <v>146.1510143845519</v>
       </c>
       <c r="D17" t="n">
-        <v>79.54639336443887</v>
+        <v>151.7849053978082</v>
       </c>
       <c r="E17" t="n">
-        <v>163.3506948364521</v>
+        <v>201.2969698739487</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>413.4426335613185</v>
+        <v>553.5620631345964</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Grid_losses</t>
+          <t>GuD</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -861,53 +861,55 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GuD</t>
+          <t>H2_storage</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>245.7507636876321</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>245.7507636876321</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>245.7507636876321</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>245.7507636876321</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>983.0030547505286</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>H2_storage</t>
+          <t>HS&lt;-&gt;East</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>245.7507636876321</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>245.7507636876321</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>245.7507636876321</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>245.7507636876321</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" t="n">
-        <v>983.0030547505286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>HS&lt;-&gt;East</t>
+          <t>HS&lt;-&gt;Middle</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -932,7 +934,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>HS&lt;-&gt;Middle</t>
+          <t>HS&lt;-&gt;North</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -957,7 +959,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>HS&lt;-&gt;North</t>
+          <t>HS&lt;-&gt;Swest</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -982,101 +984,99 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>HS&lt;-&gt;Swest</t>
+          <t>Heat storage_dist_heat</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>52.70237362453346</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>279.999467101744</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>183.0863510995083</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+        <v>255.0753517585521</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>770.8635435843379</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Heat storage_dist_heat</t>
+          <t>Heat storage_seasonal</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>81.06057348557478</v>
+        <v>467.5778634338239</v>
       </c>
       <c r="C25" t="n">
-        <v>394.2969579632468</v>
+        <v>22.06135250019848</v>
       </c>
       <c r="D25" t="n">
-        <v>176.1304167026571</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>306.9017316561487</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>958.3896798076273</v>
+        <v>489.6392159340224</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Heat storage_seasonal</t>
+          <t>Heatpump_air</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>395.0695322376739</v>
+        <v>41.38243294830917</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>132.294658750174</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>8.311078966968594</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>50.0221493813244</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>395.0695322376739</v>
+        <v>232.0103200467762</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Heatpump_air</t>
+          <t>Heatpump_recovery_heat</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34.60086007740333</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>113.3785895441962</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>19.1978486601639</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>55.19826781371314</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>222.3755660954765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Heatpump_recovery_heat</t>
+          <t>Heatpump_water</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1099,53 +1099,55 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Heatpump_water</t>
+          <t>Hydro power plant</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.6375</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>4.1345</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>6.248</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>20.85995</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>31.87995</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Hydro power plant</t>
+          <t>Import_Electricity</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6375</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>4.1345</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>6.248</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>20.85995</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
       <c r="G30" t="n">
-        <v>31.87995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Import_Electricity</t>
+          <t>Import_Gas</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1160,9 +1162,7 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Import_Gas</t>
+          <t>Import_Hydrogen</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1193,7 +1193,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Import_Hydrogen</t>
+          <t>Import_Oil</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1216,7 +1216,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Import_Oil</t>
+          <t>Import_Synthetic_fuel</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1239,53 +1239,53 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Import_Synthetic_fuel</t>
+          <t>Import_Wood</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>154.4055469997364</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>414.6727157098042</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>358.876650601929</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>686.7787974681396</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1614.733710779609</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Import_Wood</t>
+          <t>Import_brown_coal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>136.5427308328993</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>440.8343508390698</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>332.5339592787215</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>682.0211761558672</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>1591.932217106558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Import_brown_coal</t>
+          <t>Import_solid_fuel</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1308,7 +1308,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Import_solid_fuel</t>
+          <t>Li-Ion_Battery</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1331,95 +1331,95 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Li-Ion_Battery</t>
+          <t>Methanisation</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>40.68955835532322</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>72.44779380429659</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>57.75246961889792</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>78.56447658844792</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>249.4542983669656</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Methanisation</t>
+          <t>Middle&lt;-&gt;Swest</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>54.686628932528</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>98.5374019925322</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>47.48859335650499</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>106.8385277025729</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
       <c r="G40" t="n">
-        <v>307.5511519841381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Middle&lt;-&gt;Swest</t>
+          <t>Natrium_Battery</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>40.69755867816878</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1828.435760890877</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
+        <v>59.06286961656329</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1928.196189185609</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Natrium_Battery</t>
+          <t>Netzverluste</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>194.4988254859094</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>111.668616046044</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1865.903356954575</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>259.1833780501338</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>2431.254176536663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1454,20 +1454,20 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2164.025761977399</v>
+        <v>2184.383186747478</v>
       </c>
       <c r="C44" t="n">
-        <v>3479.876537291887</v>
+        <v>3467.765698995955</v>
       </c>
       <c r="D44" t="n">
         <v>2680</v>
       </c>
       <c r="E44" t="n">
-        <v>3079.092190416758</v>
+        <v>2945.082559784479</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>11402.99448968604</v>
+        <v>11277.23144552791</v>
       </c>
     </row>
     <row r="45">
@@ -1483,14 +1483,14 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1199.77840912442</v>
+        <v>1260</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>1199.77840912442</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="46">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>73.56343736328344</v>
+        <v>72.69419477343835</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>21.7545837813163</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>73.56343736328344</v>
+        <v>94.44877855475465</v>
       </c>
     </row>
     <row r="47">
@@ -1546,20 +1546,20 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>83.8479641107306</v>
+        <v>75.63106867398552</v>
       </c>
       <c r="C48" t="n">
-        <v>108.0539089735898</v>
+        <v>115.5870110433548</v>
       </c>
       <c r="D48" t="n">
         <v>100.7526510073059</v>
       </c>
       <c r="E48" t="n">
-        <v>41.87024455588045</v>
+        <v>49.05871711534573</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>334.5247686475068</v>
+        <v>341.029447839992</v>
       </c>
     </row>
     <row r="49">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2165.757140402078</v>
+        <v>1984.656798992351</v>
       </c>
       <c r="C56" t="n">
         <v>2411</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>9538.757140402078</v>
+        <v>9357.656798992351</v>
       </c>
     </row>
   </sheetData>
